--- a/data/trans_orig/IP07C18-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>24115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37553</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18294</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18887</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37747</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40293</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56218</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76744</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>28137</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53932</t>
+          <t>54430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>75017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>29412</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>36702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53387</t>
+          <t>53179</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>46668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22003</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18801</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28026</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>41810</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>532</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>95126</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>120652</t>
+          <t>119229</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>116350</t>
+          <t>115378</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>192014</t>
+          <t>192054</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>228514</t>
+          <t>228222</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>93169</t>
+          <t>92157</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>118194</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>101189</t>
+          <t>100668</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>127963</t>
+          <t>127880</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>198889</t>
+          <t>201388</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>237702</t>
+          <t>238168</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>46196</t>
+          <t>46100</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>67185</t>
+          <t>67417</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>83707</t>
+          <t>84278</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>113231</t>
+          <t>112494</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21962</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>24460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38241</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>30730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44384</t>
+          <t>45073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22574</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32840</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>32002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64787</t>
+          <t>64936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91338</t>
+          <t>91897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113329</t>
+          <t>112227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>40361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59143</t>
+          <t>59995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52404</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66928</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86531</t>
+          <t>86335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26740</t>
+          <t>26364</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57056</t>
+          <t>58372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20463</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>20583</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>148877</t>
+          <t>148810</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>178944</t>
+          <t>177482</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>142358</t>
+          <t>140255</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>169588</t>
+          <t>168806</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>300289</t>
+          <t>298591</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>340250</t>
+          <t>337869</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>77823</t>
+          <t>78699</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>104456</t>
+          <t>105976</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92015</t>
+          <t>91502</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>118218</t>
+          <t>118928</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>176543</t>
+          <t>179819</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>215577</t>
+          <t>217950</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>67596</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23334</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19138</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>38772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37009</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49796</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66898</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>56507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94314</t>
+          <t>95606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118357</t>
+          <t>119378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46621</t>
+          <t>46380</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>59890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>82307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43520</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22636</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53186</t>
+          <t>53696</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74327</t>
+          <t>74740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46316</t>
+          <t>47207</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67601</t>
+          <t>66662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>40653</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35481</t>
+          <t>35820</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>148930</t>
+          <t>148231</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>179479</t>
+          <t>179314</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>143652</t>
+          <t>141016</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>173908</t>
+          <t>172461</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>300660</t>
+          <t>301438</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>342792</t>
+          <t>342940</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>110707</t>
+          <t>109648</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>140501</t>
+          <t>138538</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>108692</t>
+          <t>109857</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>138621</t>
+          <t>139410</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227057</t>
+          <t>229485</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>268966</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>47520</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>53148</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>79741</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
